--- a/report_cards/Report_Card_Micheal_Daniel.xlsx
+++ b/report_cards/Report_Card_Micheal_Daniel.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1534,7 +1534,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Micheal_Daniel.xlsx
+++ b/report_cards/Report_Card_Micheal_Daniel.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1656,7 +1656,7 @@
       <c r="O30" s="36" t="n"/>
       <c r="P30" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q30" s="35" t="n"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Micheal_Daniel.xlsx
+++ b/report_cards/Report_Card_Micheal_Daniel.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1922,16 +1922,32 @@
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
+      <c r="G35" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>34</v>
+      </c>
       <c r="I35" s="36" t="n"/>
-      <c r="J35" s="18" t="inlineStr"/>
+      <c r="J35" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="36" t="n"/>
-      <c r="L35" s="18" t="inlineStr"/>
+      <c r="L35" s="18">
+        <f>SUM(G35, H35, J35)</f>
+        <v/>
+      </c>
       <c r="M35" s="36" t="n"/>
-      <c r="N35" s="18" t="inlineStr"/>
+      <c r="N35" s="18">
+        <f>IF(L35&gt;=75,"A1",IF(L35&gt;=70,"B2",IF(L35&gt;=65,"B3",IF(L35&gt;=60,"C4",IF(L35&gt;=55,"C5",IF(L35&gt;=50,"C6",IF(L35&gt;=45,"D7",IF(L35&gt;=40,"E8","F9"))))))))</f>
+        <v/>
+      </c>
       <c r="O35" s="36" t="n"/>
-      <c r="P35" s="18" t="inlineStr"/>
+      <c r="P35" s="42" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
       <c r="Q35" s="35" t="n"/>
       <c r="R35" s="36" t="n"/>
       <c r="T35" s="18" t="inlineStr">
@@ -2064,7 +2080,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>715</v>
+        <v>772</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2116,7 +2132,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>79.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2153,7 +2169,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>79.44%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2229,7 +2245,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2302,7 +2318,7 @@
         </is>
       </c>
       <c r="X44" s="43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y44" s="30" t="n"/>
       <c r="Z44" s="30" t="n"/>
@@ -2434,7 +2450,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>715</v>
+        <v>772</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2466,7 +2482,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>79.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2499,7 +2515,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>79.44%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2567,7 +2583,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>
@@ -2620,7 +2636,7 @@
       <c r="E54" s="35" t="n"/>
       <c r="F54" s="36" t="n"/>
       <c r="G54" s="44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H54" s="35" t="n"/>
       <c r="I54" s="35" t="n"/>

--- a/report_cards/Report_Card_Micheal_Daniel.xlsx
+++ b/report_cards/Report_Card_Micheal_Daniel.xlsx
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>

--- a/report_cards/Report_Card_Micheal_Daniel.xlsx
+++ b/report_cards/Report_Card_Micheal_Daniel.xlsx
@@ -1534,7 +1534,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>

--- a/report_cards/Report_Card_Micheal_Daniel.xlsx
+++ b/report_cards/Report_Card_Micheal_Daniel.xlsx
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1923,14 +1923,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
